--- a/02table/TableS1_sample_info.xlsx
+++ b/02table/TableS1_sample_info.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA7BBA7-92AE-F445-B917-3972D6E748CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F661EC-7F65-B44A-BC56-796E208A9D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31560" yWindow="-460" windowWidth="36480" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2652,7 +2652,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11810,7 +11809,7 @@
       </c>
     </row>
     <row r="808" spans="1:4">
-      <c r="A808" s="6" t="s">
+      <c r="A808" t="s">
         <v>803</v>
       </c>
     </row>

--- a/02table/TableS1_sample_info.xlsx
+++ b/02table/TableS1_sample_info.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F661EC-7F65-B44A-BC56-796E208A9D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553B7C5E-68A1-1541-921F-0F0046BB82E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31560" yWindow="-460" windowWidth="36480" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2364,9 +2364,6 @@
     <t>CAUMo17</t>
   </si>
   <si>
-    <t>Table S1 Hybrids and inbred lines used in this study.</t>
-  </si>
-  <si>
     <t>PA</t>
   </si>
   <si>
@@ -2515,6 +2512,9 @@
       </rPr>
       <t>In the hybrids, genotypes before and after "/" represent female and male, separately.</t>
     </r>
+  </si>
+  <si>
+    <t>Table S1. Hybrids and inbred lines used in this study.</t>
   </si>
 </sst>
 </file>
@@ -2949,21 +2949,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>777</v>
+        <v>806</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17" thickBot="1">
       <c r="A2" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2971,13 +2971,13 @@
         <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2985,13 +2985,13 @@
         <v>20837</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2999,13 +2999,13 @@
         <v>105</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3013,13 +3013,13 @@
         <v>270</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3027,13 +3027,13 @@
         <v>91</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3041,13 +3041,13 @@
         <v>2005</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3055,13 +3055,13 @@
         <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3069,13 +3069,13 @@
         <v>102</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3083,13 +3083,13 @@
         <v>4722</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3097,13 +3097,13 @@
         <v>277</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3111,13 +3111,13 @@
         <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3125,13 +3125,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3139,13 +3139,13 @@
         <v>99</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3153,13 +3153,13 @@
         <v>282</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3167,13 +3167,13 @@
         <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3181,13 +3181,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3195,13 +3195,13 @@
         <v>258</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3223,13 +3223,13 @@
         <v>658</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3237,13 +3237,13 @@
         <v>58</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3251,13 +3251,13 @@
         <v>1145</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3265,13 +3265,13 @@
         <v>236</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3279,13 +3279,13 @@
         <v>7146</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3293,13 +3293,13 @@
         <v>16</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3307,13 +3307,13 @@
         <v>1101</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3321,13 +3321,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3335,13 +3335,13 @@
         <v>244</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3349,13 +3349,13 @@
         <v>663</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3363,13 +3363,13 @@
         <v>241</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3377,13 +3377,13 @@
         <v>655</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3391,13 +3391,13 @@
         <v>52</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3405,13 +3405,13 @@
         <v>5707</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3419,13 +3419,13 @@
         <v>651</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3433,13 +3433,13 @@
         <v>254</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3447,13 +3447,13 @@
         <v>54</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3461,13 +3461,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3475,13 +3475,13 @@
         <v>604</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3489,13 +3489,13 @@
         <v>646</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3503,13 +3503,13 @@
         <v>114</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3517,13 +3517,13 @@
         <v>8</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3531,13 +3531,13 @@
         <v>298</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3545,13 +3545,13 @@
         <v>69</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3559,13 +3559,13 @@
         <v>304</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3573,13 +3573,13 @@
         <v>31</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3587,13 +3587,13 @@
         <v>116</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3601,13 +3601,13 @@
         <v>111</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3615,13 +3615,13 @@
         <v>302</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3629,13 +3629,13 @@
         <v>120</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3643,13 +3643,13 @@
         <v>20</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3657,13 +3657,13 @@
         <v>296</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3671,13 +3671,13 @@
         <v>6</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3685,13 +3685,13 @@
         <v>318</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3699,13 +3699,13 @@
         <v>22</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3713,13 +3713,13 @@
         <v>311</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3727,13 +3727,13 @@
         <v>309</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3741,13 +3741,13 @@
         <v>307</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3755,13 +3755,13 @@
         <v>313</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3769,13 +3769,13 @@
         <v>44</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3783,13 +3783,13 @@
         <v>339</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3797,13 +3797,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3811,13 +3811,13 @@
         <v>330</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3825,13 +3825,13 @@
         <v>127</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3839,13 +3839,13 @@
         <v>132</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3853,13 +3853,13 @@
         <v>26</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3867,13 +3867,13 @@
         <v>343</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3881,13 +3881,13 @@
         <v>807</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3895,13 +3895,13 @@
         <v>579</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3909,13 +3909,13 @@
         <v>693</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3923,13 +3923,13 @@
         <v>335</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3937,13 +3937,13 @@
         <v>126</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3951,13 +3951,13 @@
         <v>129</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3965,13 +3965,13 @@
         <v>346</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3979,13 +3979,13 @@
         <v>1538</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3993,13 +3993,13 @@
         <v>24</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -4007,13 +4007,13 @@
         <v>359</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -4021,13 +4021,13 @@
         <v>386</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -4035,13 +4035,13 @@
         <v>46</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -4049,13 +4049,13 @@
         <v>137</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -4063,13 +4063,13 @@
         <v>136</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -4077,13 +4077,13 @@
         <v>141</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -4091,13 +4091,13 @@
         <v>139</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -4105,13 +4105,13 @@
         <v>9058</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -4119,13 +4119,13 @@
         <v>99122</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -4133,13 +4133,13 @@
         <v>364</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -4147,13 +4147,13 @@
         <v>377</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -4161,13 +4161,13 @@
         <v>372</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -4175,13 +4175,13 @@
         <v>66</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -4189,13 +4189,13 @@
         <v>757</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -4203,13 +4203,13 @@
         <v>401</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -4217,13 +4217,13 @@
         <v>350</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -4231,13 +4231,13 @@
         <v>357</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -4245,13 +4245,13 @@
         <v>10</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -4259,13 +4259,13 @@
         <v>355</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -4273,13 +4273,13 @@
         <v>6</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -4287,13 +4287,13 @@
         <v>447</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -4301,13 +4301,13 @@
         <v>149</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4315,13 +4315,13 @@
         <v>438</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -4329,13 +4329,13 @@
         <v>442</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -4343,13 +4343,13 @@
         <v>151</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -4357,13 +4357,13 @@
         <v>434</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -4371,13 +4371,13 @@
         <v>145</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -4385,13 +4385,13 @@
         <v>419</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4399,13 +4399,13 @@
         <v>158</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4413,13 +4413,13 @@
         <v>431</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4427,13 +4427,13 @@
         <v>417</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4441,13 +4441,13 @@
         <v>8982</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4455,13 +4455,13 @@
         <v>146</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4469,13 +4469,13 @@
         <v>415</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4483,13 +4483,13 @@
         <v>12</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4497,13 +4497,13 @@
         <v>427</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4511,13 +4511,13 @@
         <v>414</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4525,13 +4525,13 @@
         <v>423</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4539,13 +4539,13 @@
         <v>71</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4553,13 +4553,13 @@
         <v>897</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4567,13 +4567,13 @@
         <v>163</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4581,13 +4581,13 @@
         <v>472</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4595,13 +4595,13 @@
         <v>483</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4609,13 +4609,13 @@
         <v>172</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4623,13 +4623,13 @@
         <v>180</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4637,13 +4637,13 @@
         <v>167</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4651,13 +4651,13 @@
         <v>161</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4665,13 +4665,13 @@
         <v>165</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4679,13 +4679,13 @@
         <v>476</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4693,13 +4693,13 @@
         <v>7236</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4707,13 +4707,13 @@
         <v>463</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4721,13 +4721,13 @@
         <v>469</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4735,13 +4735,13 @@
         <v>467</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4749,13 +4749,13 @@
         <v>465</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4763,13 +4763,13 @@
         <v>169</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4777,13 +4777,13 @@
         <v>486</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4791,13 +4791,13 @@
         <v>491</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4805,13 +4805,13 @@
         <v>176</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4819,13 +4819,13 @@
         <v>74</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4833,13 +4833,13 @@
         <v>186</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4847,13 +4847,13 @@
         <v>96201</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4861,13 +4861,13 @@
         <v>526</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4875,13 +4875,13 @@
         <v>184</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4889,13 +4889,13 @@
         <v>353</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4903,13 +4903,13 @@
         <v>64</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4917,13 +4917,13 @@
         <v>188</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4931,13 +4931,13 @@
         <v>391</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4945,13 +4945,13 @@
         <v>33</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4959,13 +4959,13 @@
         <v>532</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4973,13 +4973,13 @@
         <v>14</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4987,13 +4987,13 @@
         <v>79</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -5001,13 +5001,13 @@
         <v>530</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -5015,13 +5015,13 @@
         <v>56</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -5029,13 +5029,13 @@
         <v>9710</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -5043,13 +5043,13 @@
         <v>182</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -5057,13 +5057,13 @@
         <v>523</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -5071,13 +5071,13 @@
         <v>3335</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -5085,13 +5085,13 @@
         <v>512</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -5099,13 +5099,13 @@
         <v>519</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -5113,13 +5113,13 @@
         <v>558</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -5127,13 +5127,13 @@
         <v>214</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -5141,13 +5141,13 @@
         <v>29</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -5155,13 +5155,13 @@
         <v>217</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -5169,13 +5169,13 @@
         <v>194</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -5183,13 +5183,13 @@
         <v>76</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -5197,13 +5197,13 @@
         <v>195</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -5211,13 +5211,13 @@
         <v>581</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -5225,13 +5225,13 @@
         <v>211</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -5239,13 +5239,13 @@
         <v>208</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -5253,13 +5253,13 @@
         <v>205</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -5267,13 +5267,13 @@
         <v>35</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -5281,13 +5281,13 @@
         <v>562</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -5295,13 +5295,13 @@
         <v>785</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -5309,13 +5309,13 @@
         <v>197</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -5323,13 +5323,13 @@
         <v>556</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -5337,13 +5337,13 @@
         <v>588</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -5351,13 +5351,13 @@
         <v>554</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -5365,13 +5365,13 @@
         <v>565</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -5379,13 +5379,13 @@
         <v>549</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -5393,13 +5393,13 @@
         <v>535</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5407,13 +5407,13 @@
         <v>224</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5421,13 +5421,13 @@
         <v>226</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5435,13 +5435,13 @@
         <v>687</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5449,13 +5449,13 @@
         <v>634</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5463,13 +5463,13 @@
         <v>221</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5477,13 +5477,13 @@
         <v>748</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5491,13 +5491,13 @@
         <v>1614</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5505,13 +5505,13 @@
         <v>7327</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5519,13 +5519,13 @@
         <v>610</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5533,13 +5533,13 @@
         <v>222</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5547,13 +5547,13 @@
         <v>48</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5561,13 +5561,13 @@
         <v>594</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5575,13 +5575,13 @@
         <v>50</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5589,13 +5589,13 @@
         <v>231</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5603,13 +5603,13 @@
         <v>203</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5617,13 +5617,13 @@
         <v>607</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5631,13 +5631,13 @@
         <v>87</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5645,13 +5645,13 @@
         <v>393</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5659,13 +5659,13 @@
         <v>624</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5673,13 +5673,13 @@
         <v>773</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5687,13 +5687,13 @@
         <v>18</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5701,13 +5701,13 @@
         <v>772</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5715,13 +5715,13 @@
         <v>28</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5729,13 +5729,13 @@
         <v>1</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5743,13 +5743,13 @@
         <v>9702</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5757,13 +5757,13 @@
         <v>775</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5771,13 +5771,13 @@
         <v>60</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5785,13 +5785,13 @@
         <v>78010</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5799,13 +5799,13 @@
         <v>776</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
@@ -5823,7 +5823,7 @@
         <v>3</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
@@ -5833,7 +5833,7 @@
         <v>5</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
@@ -5843,7 +5843,7 @@
         <v>7</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
@@ -5853,7 +5853,7 @@
         <v>9</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -5863,7 +5863,7 @@
         <v>11</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
@@ -5873,7 +5873,7 @@
         <v>13</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
@@ -5883,7 +5883,7 @@
         <v>15</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
@@ -5893,7 +5893,7 @@
         <v>17</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
@@ -5903,7 +5903,7 @@
         <v>19</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -5913,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
@@ -5923,7 +5923,7 @@
         <v>23</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
@@ -5933,7 +5933,7 @@
         <v>25</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
@@ -5943,7 +5943,7 @@
         <v>27</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
@@ -5953,7 +5953,7 @@
         <v>30</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
@@ -5963,7 +5963,7 @@
         <v>32</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
@@ -5973,7 +5973,7 @@
         <v>34</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
@@ -5983,7 +5983,7 @@
         <v>36</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
@@ -5993,7 +5993,7 @@
         <v>38</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -6003,7 +6003,7 @@
         <v>40</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
@@ -6013,7 +6013,7 @@
         <v>41</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
@@ -6023,7 +6023,7 @@
         <v>42</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
@@ -6033,7 +6033,7 @@
         <v>43</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
@@ -6043,7 +6043,7 @@
         <v>45</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -6053,7 +6053,7 @@
         <v>47</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
@@ -6063,7 +6063,7 @@
         <v>49</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
@@ -6073,7 +6073,7 @@
         <v>51</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -6083,7 +6083,7 @@
         <v>53</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
@@ -6093,7 +6093,7 @@
         <v>55</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
@@ -6103,7 +6103,7 @@
         <v>57</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
@@ -6113,7 +6113,7 @@
         <v>59</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
@@ -6123,7 +6123,7 @@
         <v>62</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -6133,7 +6133,7 @@
         <v>63</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
@@ -6143,7 +6143,7 @@
         <v>65</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
@@ -6153,7 +6153,7 @@
         <v>67</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
@@ -6163,7 +6163,7 @@
         <v>68</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
@@ -6173,7 +6173,7 @@
         <v>70</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -6183,7 +6183,7 @@
         <v>72</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
@@ -6193,7 +6193,7 @@
         <v>73</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
@@ -6203,7 +6203,7 @@
         <v>75</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
@@ -6213,7 +6213,7 @@
         <v>77</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
@@ -6223,7 +6223,7 @@
         <v>78</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
@@ -6233,7 +6233,7 @@
         <v>80</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
@@ -6243,7 +6243,7 @@
         <v>82</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
@@ -6253,7 +6253,7 @@
         <v>83</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
@@ -6263,7 +6263,7 @@
         <v>84</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
@@ -6273,7 +6273,7 @@
         <v>85</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
@@ -6283,7 +6283,7 @@
         <v>86</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
@@ -6293,7 +6293,7 @@
         <v>88</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
@@ -6303,7 +6303,7 @@
         <v>89</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
@@ -6313,7 +6313,7 @@
         <v>90</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
@@ -6323,7 +6323,7 @@
         <v>92</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
@@ -6333,7 +6333,7 @@
         <v>94</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
@@ -6343,7 +6343,7 @@
         <v>96</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
@@ -6353,7 +6353,7 @@
         <v>97</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
@@ -6363,7 +6363,7 @@
         <v>98</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
@@ -6373,7 +6373,7 @@
         <v>100</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
@@ -6383,7 +6383,7 @@
         <v>101</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
@@ -6393,7 +6393,7 @@
         <v>103</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
@@ -6403,7 +6403,7 @@
         <v>104</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
@@ -6413,7 +6413,7 @@
         <v>106</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
@@ -6423,7 +6423,7 @@
         <v>107</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
@@ -6433,7 +6433,7 @@
         <v>108</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
@@ -6443,7 +6443,7 @@
         <v>110</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
@@ -6453,7 +6453,7 @@
         <v>112</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
@@ -6463,7 +6463,7 @@
         <v>113</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
@@ -6473,7 +6473,7 @@
         <v>115</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
@@ -6483,7 +6483,7 @@
         <v>117</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
@@ -6493,7 +6493,7 @@
         <v>118</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
@@ -6503,7 +6503,7 @@
         <v>119</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
@@ -6513,7 +6513,7 @@
         <v>121</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
@@ -6523,7 +6523,7 @@
         <v>122</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
@@ -6533,7 +6533,7 @@
         <v>123</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
@@ -6543,7 +6543,7 @@
         <v>124</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
@@ -6553,7 +6553,7 @@
         <v>125</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
@@ -6563,7 +6563,7 @@
         <v>128</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
@@ -6573,7 +6573,7 @@
         <v>130</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
@@ -6583,7 +6583,7 @@
         <v>131</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
@@ -6593,7 +6593,7 @@
         <v>133</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
@@ -6603,7 +6603,7 @@
         <v>134</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
@@ -6613,7 +6613,7 @@
         <v>135</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
@@ -6623,7 +6623,7 @@
         <v>138</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
@@ -6633,7 +6633,7 @@
         <v>140</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
@@ -6643,7 +6643,7 @@
         <v>142</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
@@ -6653,7 +6653,7 @@
         <v>143</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
@@ -6663,7 +6663,7 @@
         <v>144</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
@@ -6673,7 +6673,7 @@
         <v>147</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
@@ -6683,7 +6683,7 @@
         <v>148</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
@@ -6693,7 +6693,7 @@
         <v>150</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
@@ -6703,7 +6703,7 @@
         <v>152</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
@@ -6713,7 +6713,7 @@
         <v>153</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
@@ -6723,7 +6723,7 @@
         <v>154</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
@@ -6733,7 +6733,7 @@
         <v>155</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
@@ -6743,7 +6743,7 @@
         <v>156</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
@@ -6753,7 +6753,7 @@
         <v>157</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
@@ -6763,7 +6763,7 @@
         <v>159</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
@@ -6773,7 +6773,7 @@
         <v>160</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
@@ -6783,7 +6783,7 @@
         <v>162</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
@@ -6793,7 +6793,7 @@
         <v>164</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
@@ -6803,7 +6803,7 @@
         <v>166</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
@@ -6813,7 +6813,7 @@
         <v>168</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
@@ -6823,7 +6823,7 @@
         <v>170</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
@@ -6833,7 +6833,7 @@
         <v>171</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
@@ -6843,7 +6843,7 @@
         <v>173</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
@@ -6853,7 +6853,7 @@
         <v>174</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
@@ -6863,7 +6863,7 @@
         <v>175</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
@@ -6873,7 +6873,7 @@
         <v>177</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
@@ -6883,7 +6883,7 @@
         <v>178</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
@@ -6893,7 +6893,7 @@
         <v>179</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
@@ -6903,7 +6903,7 @@
         <v>181</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
@@ -6913,7 +6913,7 @@
         <v>183</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
@@ -6923,7 +6923,7 @@
         <v>185</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
@@ -6933,7 +6933,7 @@
         <v>187</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
@@ -6943,7 +6943,7 @@
         <v>189</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
@@ -6953,7 +6953,7 @@
         <v>190</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
@@ -6963,7 +6963,7 @@
         <v>191</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
@@ -6973,7 +6973,7 @@
         <v>192</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
@@ -6983,7 +6983,7 @@
         <v>193</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
@@ -6993,7 +6993,7 @@
         <v>196</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
@@ -7003,7 +7003,7 @@
         <v>198</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
@@ -7013,7 +7013,7 @@
         <v>199</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
@@ -7023,7 +7023,7 @@
         <v>200</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
@@ -7033,7 +7033,7 @@
         <v>201</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
@@ -7043,7 +7043,7 @@
         <v>202</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
@@ -7053,7 +7053,7 @@
         <v>204</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
@@ -7063,7 +7063,7 @@
         <v>206</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
@@ -7073,7 +7073,7 @@
         <v>207</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
@@ -7083,7 +7083,7 @@
         <v>209</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
@@ -7093,7 +7093,7 @@
         <v>210</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
@@ -7103,7 +7103,7 @@
         <v>212</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
@@ -7113,7 +7113,7 @@
         <v>213</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
@@ -7123,7 +7123,7 @@
         <v>215</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
@@ -7133,7 +7133,7 @@
         <v>216</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
@@ -7143,7 +7143,7 @@
         <v>218</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
@@ -7153,7 +7153,7 @@
         <v>219</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
@@ -7163,7 +7163,7 @@
         <v>220</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
@@ -7173,7 +7173,7 @@
         <v>223</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
@@ -7183,7 +7183,7 @@
         <v>225</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
@@ -7193,7 +7193,7 @@
         <v>227</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
@@ -7203,7 +7203,7 @@
         <v>228</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
@@ -7213,7 +7213,7 @@
         <v>229</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
@@ -7223,7 +7223,7 @@
         <v>230</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
@@ -7233,7 +7233,7 @@
         <v>232</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
@@ -7243,7 +7243,7 @@
         <v>233</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
@@ -7253,7 +7253,7 @@
         <v>234</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
@@ -7263,7 +7263,7 @@
         <v>235</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
@@ -7273,7 +7273,7 @@
         <v>237</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
@@ -7283,7 +7283,7 @@
         <v>238</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
@@ -7293,7 +7293,7 @@
         <v>239</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
@@ -7303,7 +7303,7 @@
         <v>240</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C355" s="3"/>
       <c r="D355" s="3"/>
@@ -7313,7 +7313,7 @@
         <v>242</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
@@ -7323,7 +7323,7 @@
         <v>243</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
@@ -7333,7 +7333,7 @@
         <v>245</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
@@ -7343,7 +7343,7 @@
         <v>246</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
@@ -7353,7 +7353,7 @@
         <v>247</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
@@ -7363,7 +7363,7 @@
         <v>248</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
@@ -7373,7 +7373,7 @@
         <v>249</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
@@ -7383,7 +7383,7 @@
         <v>250</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C363" s="3"/>
       <c r="D363" s="3"/>
@@ -7393,7 +7393,7 @@
         <v>251</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
@@ -7403,7 +7403,7 @@
         <v>252</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
@@ -7413,7 +7413,7 @@
         <v>253</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
@@ -7423,7 +7423,7 @@
         <v>255</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
@@ -7433,7 +7433,7 @@
         <v>256</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
@@ -7443,7 +7443,7 @@
         <v>257</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
@@ -7453,7 +7453,7 @@
         <v>259</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
@@ -7463,7 +7463,7 @@
         <v>260</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
@@ -7473,7 +7473,7 @@
         <v>261</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
@@ -7483,7 +7483,7 @@
         <v>262</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
@@ -7493,7 +7493,7 @@
         <v>263</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
@@ -7503,7 +7503,7 @@
         <v>264</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
@@ -7513,7 +7513,7 @@
         <v>265</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
@@ -7523,7 +7523,7 @@
         <v>266</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
@@ -7533,7 +7533,7 @@
         <v>267</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
@@ -7543,7 +7543,7 @@
         <v>268</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
@@ -7553,7 +7553,7 @@
         <v>269</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
@@ -7563,7 +7563,7 @@
         <v>271</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
@@ -7573,7 +7573,7 @@
         <v>272</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
@@ -7583,7 +7583,7 @@
         <v>273</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
@@ -7593,7 +7593,7 @@
         <v>274</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
@@ -7603,7 +7603,7 @@
         <v>275</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
@@ -7613,7 +7613,7 @@
         <v>276</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
@@ -7623,7 +7623,7 @@
         <v>278</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
@@ -7633,7 +7633,7 @@
         <v>279</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
@@ -7643,7 +7643,7 @@
         <v>280</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
@@ -7653,7 +7653,7 @@
         <v>281</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
@@ -7663,7 +7663,7 @@
         <v>283</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
@@ -7673,7 +7673,7 @@
         <v>284</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
@@ -7683,7 +7683,7 @@
         <v>285</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
@@ -7693,7 +7693,7 @@
         <v>286</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
@@ -7703,7 +7703,7 @@
         <v>287</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
@@ -7713,7 +7713,7 @@
         <v>288</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
@@ -7723,7 +7723,7 @@
         <v>289</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
@@ -7733,7 +7733,7 @@
         <v>290</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
@@ -7743,7 +7743,7 @@
         <v>291</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
@@ -7753,7 +7753,7 @@
         <v>292</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
@@ -7763,7 +7763,7 @@
         <v>293</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
@@ -7773,7 +7773,7 @@
         <v>294</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
@@ -7783,7 +7783,7 @@
         <v>295</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
@@ -7793,7 +7793,7 @@
         <v>297</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C404" s="3"/>
       <c r="D404" s="3"/>
@@ -7803,7 +7803,7 @@
         <v>299</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C405" s="3"/>
       <c r="D405" s="3"/>
@@ -7813,7 +7813,7 @@
         <v>300</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C406" s="3"/>
       <c r="D406" s="3"/>
@@ -7823,7 +7823,7 @@
         <v>301</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C407" s="3"/>
       <c r="D407" s="3"/>
@@ -7833,7 +7833,7 @@
         <v>303</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C408" s="3"/>
       <c r="D408" s="3"/>
@@ -7843,7 +7843,7 @@
         <v>305</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C409" s="3"/>
       <c r="D409" s="3"/>
@@ -7853,7 +7853,7 @@
         <v>306</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C410" s="3"/>
       <c r="D410" s="3"/>
@@ -7863,7 +7863,7 @@
         <v>308</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C411" s="3"/>
       <c r="D411" s="3"/>
@@ -7873,7 +7873,7 @@
         <v>310</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C412" s="3"/>
       <c r="D412" s="3"/>
@@ -7883,7 +7883,7 @@
         <v>312</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C413" s="3"/>
       <c r="D413" s="3"/>
@@ -7893,7 +7893,7 @@
         <v>314</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C414" s="3"/>
       <c r="D414" s="3"/>
@@ -7903,7 +7903,7 @@
         <v>315</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C415" s="3"/>
       <c r="D415" s="3"/>
@@ -7913,7 +7913,7 @@
         <v>316</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C416" s="3"/>
       <c r="D416" s="3"/>
@@ -7923,7 +7923,7 @@
         <v>317</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C417" s="3"/>
       <c r="D417" s="3"/>
@@ -7933,7 +7933,7 @@
         <v>319</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C418" s="3"/>
       <c r="D418" s="3"/>
@@ -7943,7 +7943,7 @@
         <v>320</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C419" s="3"/>
       <c r="D419" s="3"/>
@@ -7953,7 +7953,7 @@
         <v>321</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C420" s="3"/>
       <c r="D420" s="3"/>
@@ -7963,7 +7963,7 @@
         <v>322</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C421" s="3"/>
       <c r="D421" s="3"/>
@@ -7973,7 +7973,7 @@
         <v>323</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C422" s="3"/>
       <c r="D422" s="3"/>
@@ -7983,7 +7983,7 @@
         <v>324</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C423" s="3"/>
       <c r="D423" s="3"/>
@@ -7993,7 +7993,7 @@
         <v>325</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C424" s="3"/>
       <c r="D424" s="3"/>
@@ -8003,7 +8003,7 @@
         <v>326</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C425" s="3"/>
       <c r="D425" s="3"/>
@@ -8013,7 +8013,7 @@
         <v>327</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C426" s="3"/>
       <c r="D426" s="3"/>
@@ -8023,7 +8023,7 @@
         <v>328</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C427" s="3"/>
       <c r="D427" s="3"/>
@@ -8033,7 +8033,7 @@
         <v>329</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C428" s="3"/>
       <c r="D428" s="3"/>
@@ -8043,7 +8043,7 @@
         <v>331</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C429" s="3"/>
       <c r="D429" s="3"/>
@@ -8053,7 +8053,7 @@
         <v>332</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C430" s="3"/>
       <c r="D430" s="3"/>
@@ -8063,7 +8063,7 @@
         <v>333</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C431" s="3"/>
       <c r="D431" s="3"/>
@@ -8073,7 +8073,7 @@
         <v>334</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C432" s="3"/>
       <c r="D432" s="3"/>
@@ -8083,7 +8083,7 @@
         <v>336</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C433" s="3"/>
       <c r="D433" s="3"/>
@@ -8093,7 +8093,7 @@
         <v>337</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C434" s="3"/>
       <c r="D434" s="3"/>
@@ -8103,7 +8103,7 @@
         <v>338</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C435" s="3"/>
       <c r="D435" s="3"/>
@@ -8113,7 +8113,7 @@
         <v>340</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C436" s="3"/>
       <c r="D436" s="3"/>
@@ -8123,7 +8123,7 @@
         <v>341</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C437" s="3"/>
       <c r="D437" s="3"/>
@@ -8133,7 +8133,7 @@
         <v>342</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C438" s="3"/>
       <c r="D438" s="3"/>
@@ -8143,7 +8143,7 @@
         <v>344</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C439" s="3"/>
       <c r="D439" s="3"/>
@@ -8153,7 +8153,7 @@
         <v>345</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C440" s="3"/>
       <c r="D440" s="3"/>
@@ -8163,7 +8163,7 @@
         <v>347</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C441" s="3"/>
       <c r="D441" s="3"/>
@@ -8173,7 +8173,7 @@
         <v>348</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C442" s="3"/>
       <c r="D442" s="3"/>
@@ -8183,7 +8183,7 @@
         <v>349</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C443" s="3"/>
       <c r="D443" s="3"/>
@@ -8193,7 +8193,7 @@
         <v>351</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C444" s="3"/>
       <c r="D444" s="3"/>
@@ -8203,7 +8203,7 @@
         <v>352</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C445" s="3"/>
       <c r="D445" s="3"/>
@@ -8213,7 +8213,7 @@
         <v>354</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C446" s="3"/>
       <c r="D446" s="3"/>
@@ -8223,7 +8223,7 @@
         <v>356</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C447" s="3"/>
       <c r="D447" s="3"/>
@@ -8233,7 +8233,7 @@
         <v>358</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C448" s="3"/>
       <c r="D448" s="3"/>
@@ -8243,7 +8243,7 @@
         <v>360</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C449" s="3"/>
       <c r="D449" s="3"/>
@@ -8253,7 +8253,7 @@
         <v>361</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C450" s="3"/>
       <c r="D450" s="3"/>
@@ -8263,7 +8263,7 @@
         <v>362</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C451" s="3"/>
       <c r="D451" s="3"/>
@@ -8273,7 +8273,7 @@
         <v>363</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C452" s="3"/>
       <c r="D452" s="3"/>
@@ -8283,7 +8283,7 @@
         <v>365</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C453" s="3"/>
       <c r="D453" s="3"/>
@@ -8293,7 +8293,7 @@
         <v>366</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C454" s="3"/>
       <c r="D454" s="3"/>
@@ -8303,7 +8303,7 @@
         <v>367</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C455" s="3"/>
       <c r="D455" s="3"/>
@@ -8313,7 +8313,7 @@
         <v>368</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C456" s="3"/>
       <c r="D456" s="3"/>
@@ -8323,7 +8323,7 @@
         <v>369</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C457" s="3"/>
       <c r="D457" s="3"/>
@@ -8333,7 +8333,7 @@
         <v>370</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C458" s="3"/>
       <c r="D458" s="3"/>
@@ -8343,7 +8343,7 @@
         <v>371</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C459" s="3"/>
       <c r="D459" s="3"/>
@@ -8353,7 +8353,7 @@
         <v>373</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C460" s="3"/>
       <c r="D460" s="3"/>
@@ -8363,7 +8363,7 @@
         <v>374</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C461" s="3"/>
       <c r="D461" s="3"/>
@@ -8373,7 +8373,7 @@
         <v>375</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C462" s="3"/>
       <c r="D462" s="3"/>
@@ -8383,7 +8383,7 @@
         <v>376</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C463" s="3"/>
       <c r="D463" s="3"/>
@@ -8393,7 +8393,7 @@
         <v>378</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C464" s="3"/>
       <c r="D464" s="3"/>
@@ -8403,7 +8403,7 @@
         <v>379</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C465" s="3"/>
       <c r="D465" s="3"/>
@@ -8413,7 +8413,7 @@
         <v>380</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C466" s="3"/>
       <c r="D466" s="3"/>
@@ -8423,7 +8423,7 @@
         <v>381</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C467" s="3"/>
       <c r="D467" s="3"/>
@@ -8433,7 +8433,7 @@
         <v>382</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C468" s="3"/>
       <c r="D468" s="3"/>
@@ -8443,7 +8443,7 @@
         <v>383</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C469" s="3"/>
       <c r="D469" s="3"/>
@@ -8453,7 +8453,7 @@
         <v>384</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C470" s="3"/>
       <c r="D470" s="3"/>
@@ -8463,7 +8463,7 @@
         <v>385</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C471" s="3"/>
       <c r="D471" s="3"/>
@@ -8473,7 +8473,7 @@
         <v>387</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C472" s="3"/>
       <c r="D472" s="3"/>
@@ -8483,7 +8483,7 @@
         <v>388</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C473" s="3"/>
       <c r="D473" s="3"/>
@@ -8493,7 +8493,7 @@
         <v>389</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C474" s="3"/>
       <c r="D474" s="3"/>
@@ -8503,7 +8503,7 @@
         <v>390</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C475" s="3"/>
       <c r="D475" s="3"/>
@@ -8513,7 +8513,7 @@
         <v>392</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C476" s="3"/>
       <c r="D476" s="3"/>
@@ -8523,7 +8523,7 @@
         <v>394</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C477" s="3"/>
       <c r="D477" s="3"/>
@@ -8533,7 +8533,7 @@
         <v>395</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C478" s="3"/>
       <c r="D478" s="3"/>
@@ -8543,7 +8543,7 @@
         <v>396</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C479" s="3"/>
       <c r="D479" s="3"/>
@@ -8553,7 +8553,7 @@
         <v>397</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C480" s="3"/>
       <c r="D480" s="3"/>
@@ -8563,7 +8563,7 @@
         <v>398</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C481" s="3"/>
       <c r="D481" s="3"/>
@@ -8573,7 +8573,7 @@
         <v>399</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C482" s="3"/>
       <c r="D482" s="3"/>
@@ -8583,7 +8583,7 @@
         <v>400</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C483" s="3"/>
       <c r="D483" s="3"/>
@@ -8593,7 +8593,7 @@
         <v>402</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C484" s="3"/>
       <c r="D484" s="3"/>
@@ -8603,7 +8603,7 @@
         <v>403</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C485" s="3"/>
       <c r="D485" s="3"/>
@@ -8613,7 +8613,7 @@
         <v>404</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C486" s="3"/>
       <c r="D486" s="3"/>
@@ -8623,7 +8623,7 @@
         <v>405</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C487" s="3"/>
       <c r="D487" s="3"/>
@@ -8633,7 +8633,7 @@
         <v>406</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C488" s="3"/>
       <c r="D488" s="3"/>
@@ -8643,7 +8643,7 @@
         <v>407</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C489" s="3"/>
       <c r="D489" s="3"/>
@@ -8653,7 +8653,7 @@
         <v>408</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C490" s="3"/>
       <c r="D490" s="3"/>
@@ -8663,7 +8663,7 @@
         <v>409</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C491" s="3"/>
       <c r="D491" s="3"/>
@@ -8673,7 +8673,7 @@
         <v>410</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C492" s="3"/>
       <c r="D492" s="3"/>
@@ -8683,7 +8683,7 @@
         <v>411</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C493" s="3"/>
       <c r="D493" s="3"/>
@@ -8693,7 +8693,7 @@
         <v>412</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C494" s="3"/>
       <c r="D494" s="3"/>
@@ -8703,7 +8703,7 @@
         <v>413</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C495" s="3"/>
       <c r="D495" s="3"/>
@@ -8713,7 +8713,7 @@
         <v>416</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C496" s="3"/>
       <c r="D496" s="3"/>
@@ -8723,7 +8723,7 @@
         <v>418</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C497" s="3"/>
       <c r="D497" s="3"/>
@@ -8733,7 +8733,7 @@
         <v>420</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C498" s="3"/>
       <c r="D498" s="3"/>
@@ -8743,7 +8743,7 @@
         <v>421</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C499" s="3"/>
       <c r="D499" s="3"/>
@@ -8753,7 +8753,7 @@
         <v>422</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C500" s="3"/>
       <c r="D500" s="3"/>
@@ -8763,7 +8763,7 @@
         <v>424</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C501" s="3"/>
       <c r="D501" s="3"/>
@@ -8773,7 +8773,7 @@
         <v>425</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C502" s="3"/>
       <c r="D502" s="3"/>
@@ -8783,7 +8783,7 @@
         <v>426</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C503" s="3"/>
       <c r="D503" s="3"/>
@@ -8793,7 +8793,7 @@
         <v>428</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C504" s="3"/>
       <c r="D504" s="3"/>
@@ -8803,7 +8803,7 @@
         <v>429</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C505" s="3"/>
       <c r="D505" s="3"/>
@@ -8813,7 +8813,7 @@
         <v>430</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C506" s="3"/>
       <c r="D506" s="3"/>
@@ -8823,7 +8823,7 @@
         <v>432</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C507" s="3"/>
       <c r="D507" s="3"/>
@@ -8833,7 +8833,7 @@
         <v>433</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C508" s="3"/>
       <c r="D508" s="3"/>
@@ -8843,7 +8843,7 @@
         <v>435</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C509" s="3"/>
       <c r="D509" s="3"/>
@@ -8853,7 +8853,7 @@
         <v>436</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C510" s="3"/>
       <c r="D510" s="3"/>
@@ -8863,7 +8863,7 @@
         <v>437</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C511" s="3"/>
       <c r="D511" s="3"/>
@@ -8873,7 +8873,7 @@
         <v>439</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C512" s="3"/>
       <c r="D512" s="3"/>
@@ -8883,7 +8883,7 @@
         <v>440</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C513" s="3"/>
       <c r="D513" s="3"/>
@@ -8893,7 +8893,7 @@
         <v>441</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C514" s="3"/>
       <c r="D514" s="3"/>
@@ -8903,7 +8903,7 @@
         <v>443</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C515" s="3"/>
       <c r="D515" s="3"/>
@@ -8913,7 +8913,7 @@
         <v>444</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C516" s="3"/>
       <c r="D516" s="3"/>
@@ -8923,7 +8923,7 @@
         <v>445</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C517" s="3"/>
       <c r="D517" s="3"/>
@@ -8933,7 +8933,7 @@
         <v>446</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C518" s="3"/>
       <c r="D518" s="3"/>
@@ -8943,7 +8943,7 @@
         <v>448</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C519" s="3"/>
       <c r="D519" s="3"/>
@@ -8953,7 +8953,7 @@
         <v>449</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C520" s="3"/>
       <c r="D520" s="3"/>
@@ -8963,7 +8963,7 @@
         <v>450</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C521" s="3"/>
       <c r="D521" s="3"/>
@@ -8973,7 +8973,7 @@
         <v>451</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C522" s="3"/>
       <c r="D522" s="3"/>
@@ -8983,7 +8983,7 @@
         <v>452</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C523" s="3"/>
       <c r="D523" s="3"/>
@@ -8993,7 +8993,7 @@
         <v>453</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C524" s="3"/>
       <c r="D524" s="3"/>
@@ -9003,7 +9003,7 @@
         <v>454</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C525" s="3"/>
       <c r="D525" s="3"/>
@@ -9013,7 +9013,7 @@
         <v>455</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C526" s="3"/>
       <c r="D526" s="3"/>
@@ -9023,7 +9023,7 @@
         <v>456</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C527" s="3"/>
       <c r="D527" s="3"/>
@@ -9033,7 +9033,7 @@
         <v>457</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C528" s="3"/>
       <c r="D528" s="3"/>
@@ -9043,7 +9043,7 @@
         <v>458</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C529" s="3"/>
       <c r="D529" s="3"/>
@@ -9053,7 +9053,7 @@
         <v>459</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C530" s="3"/>
       <c r="D530" s="3"/>
@@ -9063,7 +9063,7 @@
         <v>460</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C531" s="3"/>
       <c r="D531" s="3"/>
@@ -9073,7 +9073,7 @@
         <v>461</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C532" s="3"/>
       <c r="D532" s="3"/>
@@ -9083,7 +9083,7 @@
         <v>462</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C533" s="3"/>
       <c r="D533" s="3"/>
@@ -9093,7 +9093,7 @@
         <v>464</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C534" s="3"/>
       <c r="D534" s="3"/>
@@ -9103,7 +9103,7 @@
         <v>466</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C535" s="3"/>
       <c r="D535" s="3"/>
@@ -9113,7 +9113,7 @@
         <v>468</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C536" s="3"/>
       <c r="D536" s="3"/>
@@ -9123,7 +9123,7 @@
         <v>470</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C537" s="3"/>
       <c r="D537" s="3"/>
@@ -9133,7 +9133,7 @@
         <v>471</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C538" s="3"/>
       <c r="D538" s="3"/>
@@ -9143,7 +9143,7 @@
         <v>473</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C539" s="3"/>
       <c r="D539" s="3"/>
@@ -9153,7 +9153,7 @@
         <v>474</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C540" s="3"/>
       <c r="D540" s="3"/>
@@ -9163,7 +9163,7 @@
         <v>475</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C541" s="3"/>
       <c r="D541" s="3"/>
@@ -9173,7 +9173,7 @@
         <v>477</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C542" s="3"/>
       <c r="D542" s="3"/>
@@ -9183,7 +9183,7 @@
         <v>478</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C543" s="3"/>
       <c r="D543" s="3"/>
@@ -9193,7 +9193,7 @@
         <v>479</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C544" s="3"/>
       <c r="D544" s="3"/>
@@ -9203,7 +9203,7 @@
         <v>480</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C545" s="3"/>
       <c r="D545" s="3"/>
@@ -9213,7 +9213,7 @@
         <v>481</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C546" s="3"/>
       <c r="D546" s="3"/>
@@ -9223,7 +9223,7 @@
         <v>482</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C547" s="3"/>
       <c r="D547" s="3"/>
@@ -9233,7 +9233,7 @@
         <v>484</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C548" s="3"/>
       <c r="D548" s="3"/>
@@ -9243,7 +9243,7 @@
         <v>485</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C549" s="3"/>
       <c r="D549" s="3"/>
@@ -9253,7 +9253,7 @@
         <v>487</v>
       </c>
       <c r="B550" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C550" s="3"/>
       <c r="D550" s="3"/>
@@ -9263,7 +9263,7 @@
         <v>488</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C551" s="3"/>
       <c r="D551" s="3"/>
@@ -9273,7 +9273,7 @@
         <v>489</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C552" s="3"/>
       <c r="D552" s="3"/>
@@ -9283,7 +9283,7 @@
         <v>490</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C553" s="3"/>
       <c r="D553" s="3"/>
@@ -9293,7 +9293,7 @@
         <v>492</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C554" s="3"/>
       <c r="D554" s="3"/>
@@ -9303,7 +9303,7 @@
         <v>493</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C555" s="3"/>
       <c r="D555" s="3"/>
@@ -9313,7 +9313,7 @@
         <v>494</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C556" s="3"/>
       <c r="D556" s="3"/>
@@ -9323,7 +9323,7 @@
         <v>495</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C557" s="3"/>
       <c r="D557" s="3"/>
@@ -9333,7 +9333,7 @@
         <v>496</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C558" s="3"/>
       <c r="D558" s="3"/>
@@ -9343,7 +9343,7 @@
         <v>497</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C559" s="3"/>
       <c r="D559" s="3"/>
@@ -9353,7 +9353,7 @@
         <v>498</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C560" s="3"/>
       <c r="D560" s="3"/>
@@ -9363,7 +9363,7 @@
         <v>499</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C561" s="3"/>
       <c r="D561" s="3"/>
@@ -9373,7 +9373,7 @@
         <v>500</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C562" s="3"/>
       <c r="D562" s="3"/>
@@ -9383,7 +9383,7 @@
         <v>501</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C563" s="3"/>
       <c r="D563" s="3"/>
@@ -9393,7 +9393,7 @@
         <v>502</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C564" s="3"/>
       <c r="D564" s="3"/>
@@ -9403,7 +9403,7 @@
         <v>503</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C565" s="3"/>
       <c r="D565" s="3"/>
@@ -9413,7 +9413,7 @@
         <v>504</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C566" s="3"/>
       <c r="D566" s="3"/>
@@ -9423,7 +9423,7 @@
         <v>505</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C567" s="3"/>
       <c r="D567" s="3"/>
@@ -9433,7 +9433,7 @@
         <v>506</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C568" s="3"/>
       <c r="D568" s="3"/>
@@ -9443,7 +9443,7 @@
         <v>507</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C569" s="3"/>
       <c r="D569" s="3"/>
@@ -9453,7 +9453,7 @@
         <v>508</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C570" s="3"/>
       <c r="D570" s="3"/>
@@ -9463,7 +9463,7 @@
         <v>509</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C571" s="3"/>
       <c r="D571" s="3"/>
@@ -9473,7 +9473,7 @@
         <v>510</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C572" s="3"/>
       <c r="D572" s="3"/>
@@ -9483,7 +9483,7 @@
         <v>511</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C573" s="3"/>
       <c r="D573" s="3"/>
@@ -9493,7 +9493,7 @@
         <v>513</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C574" s="3"/>
       <c r="D574" s="3"/>
@@ -9503,7 +9503,7 @@
         <v>514</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C575" s="3"/>
       <c r="D575" s="3"/>
@@ -9513,7 +9513,7 @@
         <v>515</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C576" s="3"/>
       <c r="D576" s="3"/>
@@ -9523,7 +9523,7 @@
         <v>516</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C577" s="3"/>
       <c r="D577" s="3"/>
@@ -9533,7 +9533,7 @@
         <v>517</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C578" s="3"/>
       <c r="D578" s="3"/>
@@ -9543,7 +9543,7 @@
         <v>518</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C579" s="3"/>
       <c r="D579" s="3"/>
@@ -9553,7 +9553,7 @@
         <v>520</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C580" s="3"/>
       <c r="D580" s="3"/>
@@ -9563,7 +9563,7 @@
         <v>521</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C581" s="3"/>
       <c r="D581" s="3"/>
@@ -9573,7 +9573,7 @@
         <v>522</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C582" s="3"/>
       <c r="D582" s="3"/>
@@ -9583,7 +9583,7 @@
         <v>524</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C583" s="3"/>
       <c r="D583" s="3"/>
@@ -9593,7 +9593,7 @@
         <v>525</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C584" s="3"/>
       <c r="D584" s="3"/>
@@ -9603,7 +9603,7 @@
         <v>527</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C585" s="3"/>
       <c r="D585" s="3"/>
@@ -9613,7 +9613,7 @@
         <v>528</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C586" s="3"/>
       <c r="D586" s="3"/>
@@ -9623,7 +9623,7 @@
         <v>529</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C587" s="3"/>
       <c r="D587" s="3"/>
@@ -9633,7 +9633,7 @@
         <v>531</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C588" s="3"/>
       <c r="D588" s="3"/>
@@ -9643,7 +9643,7 @@
         <v>533</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C589" s="3"/>
       <c r="D589" s="3"/>
@@ -9653,7 +9653,7 @@
         <v>534</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C590" s="3"/>
       <c r="D590" s="3"/>
@@ -9663,7 +9663,7 @@
         <v>536</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C591" s="3"/>
       <c r="D591" s="3"/>
@@ -9673,7 +9673,7 @@
         <v>537</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C592" s="3"/>
       <c r="D592" s="3"/>
@@ -9683,7 +9683,7 @@
         <v>538</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C593" s="3"/>
       <c r="D593" s="3"/>
@@ -9693,7 +9693,7 @@
         <v>539</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C594" s="3"/>
       <c r="D594" s="3"/>
@@ -9703,7 +9703,7 @@
         <v>540</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C595" s="3"/>
       <c r="D595" s="3"/>
@@ -9713,7 +9713,7 @@
         <v>541</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C596" s="3"/>
       <c r="D596" s="3"/>
@@ -9723,7 +9723,7 @@
         <v>542</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C597" s="3"/>
       <c r="D597" s="3"/>
@@ -9733,7 +9733,7 @@
         <v>543</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C598" s="3"/>
       <c r="D598" s="3"/>
@@ -9743,7 +9743,7 @@
         <v>544</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C599" s="3"/>
       <c r="D599" s="3"/>
@@ -9753,7 +9753,7 @@
         <v>545</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C600" s="3"/>
       <c r="D600" s="3"/>
@@ -9763,7 +9763,7 @@
         <v>546</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C601" s="3"/>
       <c r="D601" s="3"/>
@@ -9773,7 +9773,7 @@
         <v>547</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C602" s="3"/>
       <c r="D602" s="3"/>
@@ -9783,7 +9783,7 @@
         <v>548</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C603" s="3"/>
       <c r="D603" s="3"/>
@@ -9793,7 +9793,7 @@
         <v>550</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C604" s="3"/>
       <c r="D604" s="3"/>
@@ -9803,7 +9803,7 @@
         <v>551</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C605" s="3"/>
       <c r="D605" s="3"/>
@@ -9813,7 +9813,7 @@
         <v>552</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C606" s="3"/>
       <c r="D606" s="3"/>
@@ -9823,7 +9823,7 @@
         <v>553</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C607" s="3"/>
       <c r="D607" s="3"/>
@@ -9833,7 +9833,7 @@
         <v>555</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C608" s="3"/>
       <c r="D608" s="3"/>
@@ -9843,7 +9843,7 @@
         <v>557</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C609" s="3"/>
       <c r="D609" s="3"/>
@@ -9853,7 +9853,7 @@
         <v>559</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C610" s="3"/>
       <c r="D610" s="3"/>
@@ -9863,7 +9863,7 @@
         <v>560</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C611" s="3"/>
       <c r="D611" s="3"/>
@@ -9873,7 +9873,7 @@
         <v>561</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C612" s="3"/>
       <c r="D612" s="3"/>
@@ -9883,7 +9883,7 @@
         <v>563</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C613" s="3"/>
       <c r="D613" s="3"/>
@@ -9893,7 +9893,7 @@
         <v>564</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C614" s="3"/>
       <c r="D614" s="3"/>
@@ -9903,7 +9903,7 @@
         <v>566</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C615" s="3"/>
       <c r="D615" s="3"/>
@@ -9913,7 +9913,7 @@
         <v>567</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C616" s="3"/>
       <c r="D616" s="3"/>
@@ -9923,7 +9923,7 @@
         <v>568</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C617" s="3"/>
       <c r="D617" s="3"/>
@@ -9933,7 +9933,7 @@
         <v>569</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C618" s="3"/>
       <c r="D618" s="3"/>
@@ -9943,7 +9943,7 @@
         <v>570</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C619" s="3"/>
       <c r="D619" s="3"/>
@@ -9953,7 +9953,7 @@
         <v>571</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C620" s="3"/>
       <c r="D620" s="3"/>
@@ -9963,7 +9963,7 @@
         <v>572</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C621" s="3"/>
       <c r="D621" s="3"/>
@@ -9973,7 +9973,7 @@
         <v>573</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C622" s="3"/>
       <c r="D622" s="3"/>
@@ -9983,7 +9983,7 @@
         <v>574</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C623" s="3"/>
       <c r="D623" s="3"/>
@@ -9993,7 +9993,7 @@
         <v>575</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C624" s="3"/>
       <c r="D624" s="3"/>
@@ -10003,7 +10003,7 @@
         <v>576</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C625" s="3"/>
       <c r="D625" s="3"/>
@@ -10013,7 +10013,7 @@
         <v>577</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C626" s="3"/>
       <c r="D626" s="3"/>
@@ -10023,7 +10023,7 @@
         <v>578</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C627" s="3"/>
       <c r="D627" s="3"/>
@@ -10033,7 +10033,7 @@
         <v>580</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C628" s="3"/>
       <c r="D628" s="3"/>
@@ -10043,7 +10043,7 @@
         <v>582</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C629" s="3"/>
       <c r="D629" s="3"/>
@@ -10053,7 +10053,7 @@
         <v>583</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C630" s="3"/>
       <c r="D630" s="3"/>
@@ -10063,7 +10063,7 @@
         <v>584</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C631" s="3"/>
       <c r="D631" s="3"/>
@@ -10073,7 +10073,7 @@
         <v>585</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C632" s="3"/>
       <c r="D632" s="3"/>
@@ -10083,7 +10083,7 @@
         <v>586</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C633" s="3"/>
       <c r="D633" s="3"/>
@@ -10093,7 +10093,7 @@
         <v>587</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C634" s="3"/>
       <c r="D634" s="3"/>
@@ -10103,7 +10103,7 @@
         <v>589</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C635" s="3"/>
       <c r="D635" s="3"/>
@@ -10113,7 +10113,7 @@
         <v>590</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C636" s="3"/>
       <c r="D636" s="3"/>
@@ -10123,7 +10123,7 @@
         <v>591</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C637" s="3"/>
       <c r="D637" s="3"/>
@@ -10133,7 +10133,7 @@
         <v>592</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C638" s="3"/>
       <c r="D638" s="3"/>
@@ -10143,7 +10143,7 @@
         <v>593</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C639" s="3"/>
       <c r="D639" s="3"/>
@@ -10153,7 +10153,7 @@
         <v>595</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C640" s="3"/>
       <c r="D640" s="3"/>
@@ -10163,7 +10163,7 @@
         <v>596</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C641" s="3"/>
       <c r="D641" s="3"/>
@@ -10173,7 +10173,7 @@
         <v>597</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C642" s="3"/>
       <c r="D642" s="3"/>
@@ -10183,7 +10183,7 @@
         <v>598</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C643" s="3"/>
       <c r="D643" s="3"/>
@@ -10193,7 +10193,7 @@
         <v>599</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C644" s="3"/>
       <c r="D644" s="3"/>
@@ -10203,7 +10203,7 @@
         <v>600</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C645" s="3"/>
       <c r="D645" s="3"/>
@@ -10213,7 +10213,7 @@
         <v>601</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C646" s="3"/>
       <c r="D646" s="3"/>
@@ -10223,7 +10223,7 @@
         <v>602</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C647" s="3"/>
       <c r="D647" s="3"/>
@@ -10233,7 +10233,7 @@
         <v>603</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C648" s="3"/>
       <c r="D648" s="3"/>
@@ -10243,7 +10243,7 @@
         <v>605</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C649" s="3"/>
       <c r="D649" s="3"/>
@@ -10253,7 +10253,7 @@
         <v>606</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C650" s="3"/>
       <c r="D650" s="3"/>
@@ -10263,7 +10263,7 @@
         <v>608</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C651" s="3"/>
       <c r="D651" s="3"/>
@@ -10273,7 +10273,7 @@
         <v>609</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C652" s="3"/>
       <c r="D652" s="3"/>
@@ -10283,7 +10283,7 @@
         <v>611</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C653" s="3"/>
       <c r="D653" s="3"/>
@@ -10293,7 +10293,7 @@
         <v>612</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C654" s="3"/>
       <c r="D654" s="3"/>
@@ -10303,7 +10303,7 @@
         <v>613</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C655" s="3"/>
       <c r="D655" s="3"/>
@@ -10313,7 +10313,7 @@
         <v>614</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C656" s="3"/>
       <c r="D656" s="3"/>
@@ -10323,7 +10323,7 @@
         <v>615</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C657" s="3"/>
       <c r="D657" s="3"/>
@@ -10333,7 +10333,7 @@
         <v>616</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C658" s="3"/>
       <c r="D658" s="3"/>
@@ -10343,7 +10343,7 @@
         <v>617</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C659" s="3"/>
       <c r="D659" s="3"/>
@@ -10353,7 +10353,7 @@
         <v>618</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C660" s="3"/>
       <c r="D660" s="3"/>
@@ -10363,7 +10363,7 @@
         <v>619</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C661" s="3"/>
       <c r="D661" s="3"/>
@@ -10373,7 +10373,7 @@
         <v>620</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C662" s="3"/>
       <c r="D662" s="3"/>
@@ -10383,7 +10383,7 @@
         <v>621</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C663" s="3"/>
       <c r="D663" s="3"/>
@@ -10393,7 +10393,7 @@
         <v>622</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C664" s="3"/>
       <c r="D664" s="3"/>
@@ -10403,7 +10403,7 @@
         <v>623</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C665" s="3"/>
       <c r="D665" s="3"/>
@@ -10413,7 +10413,7 @@
         <v>625</v>
       </c>
       <c r="B666" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C666" s="3"/>
       <c r="D666" s="3"/>
@@ -10423,7 +10423,7 @@
         <v>626</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C667" s="3"/>
       <c r="D667" s="3"/>
@@ -10433,7 +10433,7 @@
         <v>627</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C668" s="3"/>
       <c r="D668" s="3"/>
@@ -10443,7 +10443,7 @@
         <v>628</v>
       </c>
       <c r="B669" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C669" s="3"/>
       <c r="D669" s="3"/>
@@ -10453,7 +10453,7 @@
         <v>629</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C670" s="3"/>
       <c r="D670" s="3"/>
@@ -10463,7 +10463,7 @@
         <v>630</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C671" s="3"/>
       <c r="D671" s="3"/>
@@ -10473,7 +10473,7 @@
         <v>631</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C672" s="3"/>
       <c r="D672" s="3"/>
@@ -10483,7 +10483,7 @@
         <v>632</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C673" s="3"/>
       <c r="D673" s="3"/>
@@ -10493,7 +10493,7 @@
         <v>633</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C674" s="3"/>
       <c r="D674" s="3"/>
@@ -10503,7 +10503,7 @@
         <v>635</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C675" s="3"/>
       <c r="D675" s="3"/>
@@ -10513,7 +10513,7 @@
         <v>636</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C676" s="3"/>
       <c r="D676" s="3"/>
@@ -10523,7 +10523,7 @@
         <v>637</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C677" s="3"/>
       <c r="D677" s="3"/>
@@ -10533,7 +10533,7 @@
         <v>638</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C678" s="3"/>
       <c r="D678" s="3"/>
@@ -10543,7 +10543,7 @@
         <v>639</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C679" s="3"/>
       <c r="D679" s="3"/>
@@ -10553,7 +10553,7 @@
         <v>640</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C680" s="3"/>
       <c r="D680" s="3"/>
@@ -10563,7 +10563,7 @@
         <v>641</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C681" s="3"/>
       <c r="D681" s="3"/>
@@ -10573,7 +10573,7 @@
         <v>642</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C682" s="3"/>
       <c r="D682" s="3"/>
@@ -10583,7 +10583,7 @@
         <v>643</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C683" s="3"/>
       <c r="D683" s="3"/>
@@ -10593,7 +10593,7 @@
         <v>644</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C684" s="3"/>
       <c r="D684" s="3"/>
@@ -10603,7 +10603,7 @@
         <v>645</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C685" s="3"/>
       <c r="D685" s="3"/>
@@ -10613,7 +10613,7 @@
         <v>647</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C686" s="3"/>
       <c r="D686" s="3"/>
@@ -10623,7 +10623,7 @@
         <v>648</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C687" s="3"/>
       <c r="D687" s="3"/>
@@ -10633,7 +10633,7 @@
         <v>649</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C688" s="3"/>
       <c r="D688" s="3"/>
@@ -10643,7 +10643,7 @@
         <v>650</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C689" s="3"/>
       <c r="D689" s="3"/>
@@ -10653,7 +10653,7 @@
         <v>652</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C690" s="3"/>
       <c r="D690" s="3"/>
@@ -10663,7 +10663,7 @@
         <v>653</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C691" s="3"/>
       <c r="D691" s="3"/>
@@ -10673,7 +10673,7 @@
         <v>654</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C692" s="3"/>
       <c r="D692" s="3"/>
@@ -10683,7 +10683,7 @@
         <v>656</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C693" s="3"/>
       <c r="D693" s="3"/>
@@ -10693,7 +10693,7 @@
         <v>657</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C694" s="3"/>
       <c r="D694" s="3"/>
@@ -10703,7 +10703,7 @@
         <v>659</v>
       </c>
       <c r="B695" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C695" s="3"/>
       <c r="D695" s="3"/>
@@ -10713,7 +10713,7 @@
         <v>660</v>
       </c>
       <c r="B696" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C696" s="3"/>
       <c r="D696" s="3"/>
@@ -10723,7 +10723,7 @@
         <v>661</v>
       </c>
       <c r="B697" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C697" s="3"/>
       <c r="D697" s="3"/>
@@ -10733,7 +10733,7 @@
         <v>662</v>
       </c>
       <c r="B698" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C698" s="3"/>
       <c r="D698" s="3"/>
@@ -10743,7 +10743,7 @@
         <v>664</v>
       </c>
       <c r="B699" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C699" s="3"/>
       <c r="D699" s="3"/>
@@ -10753,7 +10753,7 @@
         <v>665</v>
       </c>
       <c r="B700" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C700" s="3"/>
       <c r="D700" s="3"/>
@@ -10763,7 +10763,7 @@
         <v>666</v>
       </c>
       <c r="B701" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C701" s="3"/>
       <c r="D701" s="3"/>
@@ -10773,7 +10773,7 @@
         <v>667</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C702" s="3"/>
       <c r="D702" s="3"/>
@@ -10783,7 +10783,7 @@
         <v>668</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C703" s="3"/>
       <c r="D703" s="3"/>
@@ -10793,7 +10793,7 @@
         <v>669</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C704" s="3"/>
       <c r="D704" s="3"/>
@@ -10803,7 +10803,7 @@
         <v>670</v>
       </c>
       <c r="B705" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C705" s="3"/>
       <c r="D705" s="3"/>
@@ -10813,7 +10813,7 @@
         <v>671</v>
       </c>
       <c r="B706" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C706" s="3"/>
       <c r="D706" s="3"/>
@@ -10823,7 +10823,7 @@
         <v>672</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C707" s="3"/>
       <c r="D707" s="3"/>
@@ -10833,7 +10833,7 @@
         <v>673</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C708" s="3"/>
       <c r="D708" s="3"/>
@@ -10843,7 +10843,7 @@
         <v>674</v>
       </c>
       <c r="B709" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C709" s="3"/>
       <c r="D709" s="3"/>
@@ -10853,7 +10853,7 @@
         <v>675</v>
       </c>
       <c r="B710" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C710" s="3"/>
       <c r="D710" s="3"/>
@@ -10863,7 +10863,7 @@
         <v>676</v>
       </c>
       <c r="B711" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C711" s="3"/>
       <c r="D711" s="3"/>
@@ -10873,7 +10873,7 @@
         <v>677</v>
       </c>
       <c r="B712" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C712" s="3"/>
       <c r="D712" s="3"/>
@@ -10883,7 +10883,7 @@
         <v>678</v>
       </c>
       <c r="B713" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C713" s="3"/>
       <c r="D713" s="3"/>
@@ -10893,7 +10893,7 @@
         <v>679</v>
       </c>
       <c r="B714" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C714" s="3"/>
       <c r="D714" s="3"/>
@@ -10903,7 +10903,7 @@
         <v>680</v>
       </c>
       <c r="B715" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C715" s="3"/>
       <c r="D715" s="3"/>
@@ -10913,7 +10913,7 @@
         <v>681</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C716" s="3"/>
       <c r="D716" s="3"/>
@@ -10923,7 +10923,7 @@
         <v>682</v>
       </c>
       <c r="B717" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C717" s="3"/>
       <c r="D717" s="3"/>
@@ -10933,7 +10933,7 @@
         <v>683</v>
       </c>
       <c r="B718" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C718" s="3"/>
       <c r="D718" s="3"/>
@@ -10943,7 +10943,7 @@
         <v>684</v>
       </c>
       <c r="B719" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C719" s="3"/>
       <c r="D719" s="3"/>
@@ -10953,7 +10953,7 @@
         <v>685</v>
       </c>
       <c r="B720" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C720" s="3"/>
       <c r="D720" s="3"/>
@@ -10963,7 +10963,7 @@
         <v>686</v>
       </c>
       <c r="B721" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C721" s="3"/>
       <c r="D721" s="3"/>
@@ -10973,7 +10973,7 @@
         <v>688</v>
       </c>
       <c r="B722" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C722" s="3"/>
       <c r="D722" s="3"/>
@@ -10983,7 +10983,7 @@
         <v>689</v>
       </c>
       <c r="B723" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C723" s="3"/>
       <c r="D723" s="3"/>
@@ -10993,7 +10993,7 @@
         <v>690</v>
       </c>
       <c r="B724" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C724" s="3"/>
       <c r="D724" s="3"/>
@@ -11003,7 +11003,7 @@
         <v>691</v>
       </c>
       <c r="B725" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C725" s="3"/>
       <c r="D725" s="3"/>
@@ -11013,7 +11013,7 @@
         <v>692</v>
       </c>
       <c r="B726" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C726" s="3"/>
       <c r="D726" s="3"/>
@@ -11023,7 +11023,7 @@
         <v>694</v>
       </c>
       <c r="B727" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C727" s="3"/>
       <c r="D727" s="3"/>
@@ -11033,7 +11033,7 @@
         <v>695</v>
       </c>
       <c r="B728" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C728" s="3"/>
       <c r="D728" s="3"/>
@@ -11043,7 +11043,7 @@
         <v>696</v>
       </c>
       <c r="B729" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C729" s="3"/>
       <c r="D729" s="3"/>
@@ -11053,7 +11053,7 @@
         <v>697</v>
       </c>
       <c r="B730" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C730" s="3"/>
       <c r="D730" s="3"/>
@@ -11063,7 +11063,7 @@
         <v>698</v>
       </c>
       <c r="B731" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C731" s="3"/>
       <c r="D731" s="3"/>
@@ -11073,7 +11073,7 @@
         <v>699</v>
       </c>
       <c r="B732" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C732" s="3"/>
       <c r="D732" s="3"/>
@@ -11083,7 +11083,7 @@
         <v>700</v>
       </c>
       <c r="B733" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C733" s="3"/>
       <c r="D733" s="3"/>
@@ -11093,7 +11093,7 @@
         <v>701</v>
       </c>
       <c r="B734" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C734" s="3"/>
       <c r="D734" s="3"/>
@@ -11103,7 +11103,7 @@
         <v>702</v>
       </c>
       <c r="B735" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C735" s="3"/>
       <c r="D735" s="3"/>
@@ -11113,7 +11113,7 @@
         <v>703</v>
       </c>
       <c r="B736" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C736" s="3"/>
       <c r="D736" s="3"/>
@@ -11123,7 +11123,7 @@
         <v>704</v>
       </c>
       <c r="B737" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C737" s="3"/>
       <c r="D737" s="3"/>
@@ -11133,7 +11133,7 @@
         <v>705</v>
       </c>
       <c r="B738" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C738" s="3"/>
       <c r="D738" s="3"/>
@@ -11143,7 +11143,7 @@
         <v>706</v>
       </c>
       <c r="B739" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C739" s="3"/>
       <c r="D739" s="3"/>
@@ -11153,7 +11153,7 @@
         <v>707</v>
       </c>
       <c r="B740" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C740" s="3"/>
       <c r="D740" s="3"/>
@@ -11163,7 +11163,7 @@
         <v>708</v>
       </c>
       <c r="B741" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C741" s="3"/>
       <c r="D741" s="3"/>
@@ -11173,7 +11173,7 @@
         <v>709</v>
       </c>
       <c r="B742" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C742" s="3"/>
       <c r="D742" s="3"/>
@@ -11183,7 +11183,7 @@
         <v>710</v>
       </c>
       <c r="B743" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C743" s="3"/>
       <c r="D743" s="3"/>
@@ -11193,7 +11193,7 @@
         <v>711</v>
       </c>
       <c r="B744" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C744" s="3"/>
       <c r="D744" s="3"/>
@@ -11203,7 +11203,7 @@
         <v>712</v>
       </c>
       <c r="B745" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C745" s="3"/>
       <c r="D745" s="3"/>
@@ -11213,7 +11213,7 @@
         <v>713</v>
       </c>
       <c r="B746" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C746" s="3"/>
       <c r="D746" s="3"/>
@@ -11223,7 +11223,7 @@
         <v>714</v>
       </c>
       <c r="B747" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C747" s="3"/>
       <c r="D747" s="3"/>
@@ -11233,7 +11233,7 @@
         <v>715</v>
       </c>
       <c r="B748" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C748" s="3"/>
       <c r="D748" s="3"/>
@@ -11243,7 +11243,7 @@
         <v>716</v>
       </c>
       <c r="B749" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C749" s="3"/>
       <c r="D749" s="3"/>
@@ -11253,7 +11253,7 @@
         <v>717</v>
       </c>
       <c r="B750" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C750" s="3"/>
       <c r="D750" s="3"/>
@@ -11263,7 +11263,7 @@
         <v>718</v>
       </c>
       <c r="B751" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C751" s="3"/>
       <c r="D751" s="3"/>
@@ -11273,7 +11273,7 @@
         <v>719</v>
       </c>
       <c r="B752" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C752" s="3"/>
       <c r="D752" s="3"/>
@@ -11283,7 +11283,7 @@
         <v>720</v>
       </c>
       <c r="B753" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C753" s="3"/>
       <c r="D753" s="3"/>
@@ -11293,7 +11293,7 @@
         <v>721</v>
       </c>
       <c r="B754" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C754" s="3"/>
       <c r="D754" s="3"/>
@@ -11303,7 +11303,7 @@
         <v>722</v>
       </c>
       <c r="B755" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C755" s="3"/>
       <c r="D755" s="3"/>
@@ -11313,7 +11313,7 @@
         <v>723</v>
       </c>
       <c r="B756" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C756" s="3"/>
       <c r="D756" s="3"/>
@@ -11323,7 +11323,7 @@
         <v>724</v>
       </c>
       <c r="B757" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C757" s="3"/>
       <c r="D757" s="3"/>
@@ -11333,7 +11333,7 @@
         <v>725</v>
       </c>
       <c r="B758" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C758" s="3"/>
       <c r="D758" s="3"/>
@@ -11343,7 +11343,7 @@
         <v>726</v>
       </c>
       <c r="B759" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C759" s="3"/>
       <c r="D759" s="3"/>
@@ -11353,7 +11353,7 @@
         <v>727</v>
       </c>
       <c r="B760" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C760" s="3"/>
       <c r="D760" s="3"/>
@@ -11363,7 +11363,7 @@
         <v>728</v>
       </c>
       <c r="B761" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C761" s="3"/>
       <c r="D761" s="3"/>
@@ -11373,7 +11373,7 @@
         <v>729</v>
       </c>
       <c r="B762" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C762" s="3"/>
       <c r="D762" s="3"/>
@@ -11383,7 +11383,7 @@
         <v>730</v>
       </c>
       <c r="B763" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C763" s="3"/>
       <c r="D763" s="3"/>
@@ -11393,7 +11393,7 @@
         <v>731</v>
       </c>
       <c r="B764" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C764" s="3"/>
       <c r="D764" s="3"/>
@@ -11403,7 +11403,7 @@
         <v>732</v>
       </c>
       <c r="B765" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C765" s="3"/>
       <c r="D765" s="3"/>
@@ -11413,7 +11413,7 @@
         <v>733</v>
       </c>
       <c r="B766" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C766" s="3"/>
       <c r="D766" s="3"/>
@@ -11423,7 +11423,7 @@
         <v>734</v>
       </c>
       <c r="B767" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C767" s="3"/>
       <c r="D767" s="3"/>
@@ -11433,7 +11433,7 @@
         <v>735</v>
       </c>
       <c r="B768" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C768" s="3"/>
       <c r="D768" s="3"/>
@@ -11443,7 +11443,7 @@
         <v>736</v>
       </c>
       <c r="B769" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C769" s="3"/>
       <c r="D769" s="3"/>
@@ -11453,7 +11453,7 @@
         <v>737</v>
       </c>
       <c r="B770" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C770" s="3"/>
       <c r="D770" s="3"/>
@@ -11463,7 +11463,7 @@
         <v>738</v>
       </c>
       <c r="B771" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C771" s="3"/>
       <c r="D771" s="3"/>
@@ -11473,7 +11473,7 @@
         <v>739</v>
       </c>
       <c r="B772" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C772" s="3"/>
       <c r="D772" s="3"/>
@@ -11483,7 +11483,7 @@
         <v>740</v>
       </c>
       <c r="B773" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C773" s="3"/>
       <c r="D773" s="3"/>
@@ -11493,7 +11493,7 @@
         <v>741</v>
       </c>
       <c r="B774" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C774" s="3"/>
       <c r="D774" s="3"/>
@@ -11503,7 +11503,7 @@
         <v>742</v>
       </c>
       <c r="B775" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C775" s="3"/>
       <c r="D775" s="3"/>
@@ -11513,7 +11513,7 @@
         <v>743</v>
       </c>
       <c r="B776" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C776" s="3"/>
       <c r="D776" s="3"/>
@@ -11523,7 +11523,7 @@
         <v>744</v>
       </c>
       <c r="B777" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C777" s="3"/>
       <c r="D777" s="3"/>
@@ -11533,7 +11533,7 @@
         <v>745</v>
       </c>
       <c r="B778" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C778" s="3"/>
       <c r="D778" s="3"/>
@@ -11543,7 +11543,7 @@
         <v>746</v>
       </c>
       <c r="B779" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C779" s="3"/>
       <c r="D779" s="3"/>
@@ -11553,7 +11553,7 @@
         <v>747</v>
       </c>
       <c r="B780" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C780" s="3"/>
       <c r="D780" s="3"/>
@@ -11563,7 +11563,7 @@
         <v>749</v>
       </c>
       <c r="B781" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C781" s="3"/>
       <c r="D781" s="3"/>
@@ -11573,7 +11573,7 @@
         <v>750</v>
       </c>
       <c r="B782" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C782" s="3"/>
       <c r="D782" s="3"/>
@@ -11583,7 +11583,7 @@
         <v>751</v>
       </c>
       <c r="B783" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C783" s="3"/>
       <c r="D783" s="3"/>
@@ -11593,7 +11593,7 @@
         <v>752</v>
       </c>
       <c r="B784" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C784" s="3"/>
       <c r="D784" s="3"/>
@@ -11603,7 +11603,7 @@
         <v>753</v>
       </c>
       <c r="B785" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C785" s="3"/>
       <c r="D785" s="3"/>
@@ -11613,7 +11613,7 @@
         <v>754</v>
       </c>
       <c r="B786" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C786" s="3"/>
       <c r="D786" s="3"/>
@@ -11623,7 +11623,7 @@
         <v>755</v>
       </c>
       <c r="B787" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C787" s="3"/>
       <c r="D787" s="3"/>
@@ -11633,7 +11633,7 @@
         <v>756</v>
       </c>
       <c r="B788" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C788" s="3"/>
       <c r="D788" s="3"/>
@@ -11643,7 +11643,7 @@
         <v>757</v>
       </c>
       <c r="B789" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C789" s="3"/>
       <c r="D789" s="3"/>
@@ -11653,7 +11653,7 @@
         <v>758</v>
       </c>
       <c r="B790" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C790" s="3"/>
       <c r="D790" s="3"/>
@@ -11663,7 +11663,7 @@
         <v>759</v>
       </c>
       <c r="B791" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C791" s="3"/>
       <c r="D791" s="3"/>
@@ -11673,7 +11673,7 @@
         <v>760</v>
       </c>
       <c r="B792" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C792" s="3"/>
       <c r="D792" s="3"/>
@@ -11683,7 +11683,7 @@
         <v>761</v>
       </c>
       <c r="B793" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C793" s="3"/>
       <c r="D793" s="3"/>
@@ -11693,7 +11693,7 @@
         <v>762</v>
       </c>
       <c r="B794" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C794" s="3"/>
       <c r="D794" s="3"/>
@@ -11703,7 +11703,7 @@
         <v>763</v>
       </c>
       <c r="B795" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C795" s="3"/>
       <c r="D795" s="3"/>
@@ -11713,7 +11713,7 @@
         <v>764</v>
       </c>
       <c r="B796" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C796" s="3"/>
       <c r="D796" s="3"/>
@@ -11723,7 +11723,7 @@
         <v>765</v>
       </c>
       <c r="B797" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C797" s="3"/>
       <c r="D797" s="3"/>
@@ -11733,7 +11733,7 @@
         <v>766</v>
       </c>
       <c r="B798" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C798" s="3"/>
       <c r="D798" s="3"/>
@@ -11743,7 +11743,7 @@
         <v>767</v>
       </c>
       <c r="B799" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C799" s="3"/>
       <c r="D799" s="3"/>
@@ -11753,7 +11753,7 @@
         <v>768</v>
       </c>
       <c r="B800" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C800" s="3"/>
       <c r="D800" s="3"/>
@@ -11763,7 +11763,7 @@
         <v>769</v>
       </c>
       <c r="B801" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C801" s="3"/>
       <c r="D801" s="3"/>
@@ -11773,7 +11773,7 @@
         <v>770</v>
       </c>
       <c r="B802" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C802" s="3"/>
       <c r="D802" s="3"/>
@@ -11783,7 +11783,7 @@
         <v>771</v>
       </c>
       <c r="B803" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C803" s="3"/>
       <c r="D803" s="3"/>
@@ -11793,34 +11793,34 @@
         <v>774</v>
       </c>
       <c r="B804" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C804" s="4"/>
       <c r="D804" s="4"/>
     </row>
     <row r="806" spans="1:4" ht="16">
       <c r="A806" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="807" spans="1:4" ht="16">
       <c r="A807" s="5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="808" spans="1:4">
       <c r="A808" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="809" spans="1:4">
       <c r="A809" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="810" spans="1:4">
       <c r="A810" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
